--- a/Live_births_married_out-of-wedlock_districts_municipalities_and_place_of_residence.xlsx
+++ b/Live_births_married_out-of-wedlock_districts_municipalities_and_place_of_residence.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sasho kravaikov\Desktop\live_births\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3C1D57-B6B8-4887-ACA9-09C36A44970F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C62FAD-BCD1-4F74-AA7F-AB4B42F344DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14250" yWindow="3180" windowWidth="14115" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="277">
   <si>
     <t>Области Общини</t>
   </si>
@@ -629,12 +629,6 @@
   </si>
   <si>
     <t>Чепеларе</t>
-  </si>
-  <si>
-    <t>София (столица)</t>
-  </si>
-  <si>
-    <t>Столична</t>
   </si>
   <si>
     <t>София</t>
@@ -1215,7 +1209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J295"/>
+  <dimension ref="A1:J294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="54" customWidth="1"/>
@@ -1226,31 +1220,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -8390,1460 +8384,1460 @@
       </c>
     </row>
     <row r="225" spans="1:10">
-      <c r="A225" t="s">
+      <c r="A225" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B225" s="1">
+        <v>1927</v>
+      </c>
+      <c r="C225" s="1">
+        <v>632</v>
+      </c>
+      <c r="D225" s="1">
+        <v>1295</v>
+      </c>
+      <c r="E225" s="1">
+        <v>1249</v>
+      </c>
+      <c r="F225" s="1">
+        <v>424</v>
+      </c>
+      <c r="G225" s="1">
+        <v>825</v>
+      </c>
+      <c r="H225" s="1">
+        <v>678</v>
+      </c>
+      <c r="I225" s="1">
+        <v>208</v>
+      </c>
+      <c r="J225" s="1">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10">
+      <c r="A226" t="s">
         <v>204</v>
       </c>
-      <c r="B225" s="3">
-        <v>12025</v>
-      </c>
-      <c r="C225" s="3">
-        <v>5586</v>
-      </c>
-      <c r="D225" s="3">
-        <v>6439</v>
-      </c>
-      <c r="E225" s="3">
-        <v>11589</v>
-      </c>
-      <c r="F225" s="3">
-        <v>5387</v>
-      </c>
-      <c r="G225" s="3">
-        <v>6202</v>
-      </c>
-      <c r="H225" s="3">
-        <v>436</v>
-      </c>
-      <c r="I225" s="3">
-        <v>199</v>
-      </c>
-      <c r="J225" s="3">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="226" spans="1:10">
-      <c r="A226" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B226" s="1">
-        <v>1927</v>
-      </c>
-      <c r="C226" s="1">
-        <v>632</v>
-      </c>
-      <c r="D226" s="1">
-        <v>1295</v>
-      </c>
-      <c r="E226" s="1">
-        <v>1249</v>
-      </c>
-      <c r="F226" s="1">
-        <v>424</v>
-      </c>
-      <c r="G226" s="1">
-        <v>825</v>
-      </c>
-      <c r="H226" s="1">
-        <v>678</v>
-      </c>
-      <c r="I226" s="1">
-        <v>208</v>
-      </c>
-      <c r="J226" s="1">
-        <v>470</v>
+      <c r="B226" s="3">
+        <v>17</v>
+      </c>
+      <c r="C226" s="3">
+        <v>4</v>
+      </c>
+      <c r="D226" s="3">
+        <v>13</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H226" s="3">
+        <v>17</v>
+      </c>
+      <c r="I226" s="3">
+        <v>4</v>
+      </c>
+      <c r="J226" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="227" spans="1:10">
       <c r="A227" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B227" s="3">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="C227" s="3">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D227" s="3">
-        <v>13</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G227" s="2" t="s">
-        <v>4</v>
+        <v>47</v>
+      </c>
+      <c r="E227" s="3">
+        <v>63</v>
+      </c>
+      <c r="F227" s="3">
+        <v>23</v>
+      </c>
+      <c r="G227" s="3">
+        <v>40</v>
       </c>
       <c r="H227" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I227" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J227" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:10">
       <c r="A228" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B228" s="3">
+        <v>254</v>
+      </c>
+      <c r="C228" s="3">
+        <v>68</v>
+      </c>
+      <c r="D228" s="3">
+        <v>186</v>
+      </c>
+      <c r="E228" s="3">
+        <v>153</v>
+      </c>
+      <c r="F228" s="3">
+        <v>46</v>
+      </c>
+      <c r="G228" s="3">
+        <v>107</v>
+      </c>
+      <c r="H228" s="3">
+        <v>101</v>
+      </c>
+      <c r="I228" s="3">
+        <v>22</v>
+      </c>
+      <c r="J228" s="3">
         <v>79</v>
-      </c>
-      <c r="C228" s="3">
-        <v>32</v>
-      </c>
-      <c r="D228" s="3">
-        <v>47</v>
-      </c>
-      <c r="E228" s="3">
-        <v>63</v>
-      </c>
-      <c r="F228" s="3">
-        <v>23</v>
-      </c>
-      <c r="G228" s="3">
-        <v>40</v>
-      </c>
-      <c r="H228" s="3">
-        <v>16</v>
-      </c>
-      <c r="I228" s="3">
-        <v>9</v>
-      </c>
-      <c r="J228" s="3">
-        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:10">
       <c r="A229" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B229" s="3">
-        <v>254</v>
-      </c>
-      <c r="C229" s="3">
-        <v>68</v>
-      </c>
-      <c r="D229" s="3">
-        <v>186</v>
-      </c>
-      <c r="E229" s="3">
-        <v>153</v>
-      </c>
-      <c r="F229" s="3">
-        <v>46</v>
-      </c>
-      <c r="G229" s="3">
-        <v>107</v>
+        <v>29</v>
+      </c>
+      <c r="C229" t="s">
+        <v>35</v>
+      </c>
+      <c r="D229" t="s">
+        <v>35</v>
+      </c>
+      <c r="E229" t="s">
+        <v>35</v>
+      </c>
+      <c r="F229" t="s">
+        <v>35</v>
+      </c>
+      <c r="G229" t="s">
+        <v>35</v>
       </c>
       <c r="H229" s="3">
-        <v>101</v>
-      </c>
-      <c r="I229" s="3">
-        <v>22</v>
-      </c>
-      <c r="J229" s="3">
-        <v>79</v>
+        <v>3</v>
+      </c>
+      <c r="I229" t="s">
+        <v>35</v>
+      </c>
+      <c r="J229" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="230" spans="1:10">
       <c r="A230" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B230" s="3">
-        <v>29</v>
-      </c>
-      <c r="C230" t="s">
-        <v>35</v>
-      </c>
-      <c r="D230" t="s">
-        <v>35</v>
-      </c>
-      <c r="E230" t="s">
-        <v>35</v>
-      </c>
-      <c r="F230" t="s">
-        <v>35</v>
-      </c>
-      <c r="G230" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="C230" s="3">
+        <v>14</v>
+      </c>
+      <c r="D230" s="3">
+        <v>33</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H230" s="3">
-        <v>3</v>
-      </c>
-      <c r="I230" t="s">
-        <v>35</v>
-      </c>
-      <c r="J230" t="s">
-        <v>35</v>
+        <v>47</v>
+      </c>
+      <c r="I230" s="3">
+        <v>14</v>
+      </c>
+      <c r="J230" s="3">
+        <v>33</v>
       </c>
     </row>
     <row r="231" spans="1:10">
       <c r="A231" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B231" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C231" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D231" s="3">
-        <v>33</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G231" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H231" s="3">
-        <v>47</v>
-      </c>
-      <c r="I231" s="3">
-        <v>14</v>
-      </c>
-      <c r="J231" s="3">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="E231" s="3">
+        <v>44</v>
+      </c>
+      <c r="F231" s="3">
+        <v>12</v>
+      </c>
+      <c r="G231" s="3">
+        <v>32</v>
+      </c>
+      <c r="H231" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I231" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J231" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="232" spans="1:10">
       <c r="A232" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B232" s="3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C232" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D232" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E232" s="3">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F232" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G232" s="3">
-        <v>32</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I232" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J232" s="2" t="s">
-        <v>4</v>
+        <v>17</v>
+      </c>
+      <c r="H232" s="3">
+        <v>17</v>
+      </c>
+      <c r="I232" s="3">
+        <v>3</v>
+      </c>
+      <c r="J232" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="233" spans="1:10">
       <c r="A233" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B233" s="3">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="C233" s="3">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="D233" s="3">
+        <v>111</v>
+      </c>
+      <c r="E233" s="3">
+        <v>58</v>
+      </c>
+      <c r="F233" s="3">
+        <v>27</v>
+      </c>
+      <c r="G233" s="3">
         <v>31</v>
       </c>
-      <c r="E233" s="3">
-        <v>25</v>
-      </c>
-      <c r="F233" s="3">
-        <v>8</v>
-      </c>
-      <c r="G233" s="3">
-        <v>17</v>
-      </c>
       <c r="H233" s="3">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="I233" s="3">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="J233" s="3">
-        <v>14</v>
+        <v>80</v>
       </c>
     </row>
     <row r="234" spans="1:10">
       <c r="A234" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B234" s="3">
-        <v>201</v>
+        <v>89</v>
       </c>
       <c r="C234" s="3">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="D234" s="3">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="E234" s="3">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F234" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G234" s="3">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H234" s="3">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="I234" s="3">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="J234" s="3">
-        <v>80</v>
+        <v>16</v>
       </c>
     </row>
     <row r="235" spans="1:10">
       <c r="A235" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B235" s="3">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="C235" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="D235" s="3">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="E235" s="3">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="F235" s="3">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G235" s="3">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H235" s="3">
-        <v>19</v>
-      </c>
-      <c r="I235" s="3">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="I235" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="J235" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:10">
       <c r="A236" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B236" s="3">
-        <v>32</v>
+        <v>235</v>
       </c>
       <c r="C236" s="3">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="D236" s="3">
-        <v>22</v>
+        <v>177</v>
       </c>
       <c r="E236" s="3">
-        <v>27</v>
+        <v>201</v>
       </c>
       <c r="F236" s="3">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="G236" s="3">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="H236" s="3">
-        <v>5</v>
-      </c>
-      <c r="I236" s="2" t="s">
-        <v>4</v>
+        <v>34</v>
+      </c>
+      <c r="I236" s="3">
+        <v>11</v>
       </c>
       <c r="J236" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:10">
       <c r="A237" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B237" s="3">
-        <v>235</v>
-      </c>
-      <c r="C237" s="3">
-        <v>58</v>
+        <v>5</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="D237" s="3">
-        <v>177</v>
+        <v>5</v>
       </c>
       <c r="E237" s="3">
-        <v>201</v>
-      </c>
-      <c r="F237" s="3">
-        <v>47</v>
+        <v>5</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="G237" s="3">
-        <v>154</v>
-      </c>
-      <c r="H237" s="3">
-        <v>34</v>
-      </c>
-      <c r="I237" s="3">
-        <v>11</v>
-      </c>
-      <c r="J237" s="3">
-        <v>23</v>
+        <v>5</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I237" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J237" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="238" spans="1:10">
       <c r="A238" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B238" s="3">
-        <v>5</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>4</v>
+        <v>68</v>
+      </c>
+      <c r="C238" s="3">
+        <v>28</v>
       </c>
       <c r="D238" s="3">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E238" s="3">
-        <v>5</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>4</v>
+        <v>35</v>
+      </c>
+      <c r="F238" s="3">
+        <v>15</v>
       </c>
       <c r="G238" s="3">
-        <v>5</v>
-      </c>
-      <c r="H238" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I238" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J238" s="2" t="s">
-        <v>4</v>
+        <v>20</v>
+      </c>
+      <c r="H238" s="3">
+        <v>33</v>
+      </c>
+      <c r="I238" s="3">
+        <v>13</v>
+      </c>
+      <c r="J238" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="239" spans="1:10">
       <c r="A239" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B239" s="3">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="C239" s="3">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D239" s="3">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E239" s="3">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="F239" s="3">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="G239" s="3">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H239" s="3">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I239" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J239" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:10">
       <c r="A240" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B240" s="3">
-        <v>129</v>
+        <v>10</v>
       </c>
       <c r="C240" s="3">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="D240" s="3">
-        <v>66</v>
-      </c>
-      <c r="E240" s="3">
-        <v>92</v>
-      </c>
-      <c r="F240" s="3">
-        <v>49</v>
-      </c>
-      <c r="G240" s="3">
-        <v>43</v>
+        <v>7</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H240" s="3">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="I240" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J240" s="3">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241" spans="1:10">
       <c r="A241" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B241" s="3">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C241" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D241" s="3">
-        <v>7</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G241" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H241" s="3">
-        <v>10</v>
-      </c>
-      <c r="I241" s="3">
-        <v>3</v>
-      </c>
-      <c r="J241" s="3">
-        <v>7</v>
+        <v>37</v>
+      </c>
+      <c r="E241" t="s">
+        <v>35</v>
+      </c>
+      <c r="F241" t="s">
+        <v>35</v>
+      </c>
+      <c r="G241" t="s">
+        <v>35</v>
+      </c>
+      <c r="H241" t="s">
+        <v>35</v>
+      </c>
+      <c r="I241" t="s">
+        <v>35</v>
+      </c>
+      <c r="J241" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="242" spans="1:10">
       <c r="A242" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B242" s="3">
+        <v>85</v>
+      </c>
+      <c r="C242" s="3">
+        <v>16</v>
+      </c>
+      <c r="D242" s="3">
+        <v>69</v>
+      </c>
+      <c r="E242" s="3">
+        <v>31</v>
+      </c>
+      <c r="F242" s="3">
+        <v>10</v>
+      </c>
+      <c r="G242" s="3">
+        <v>21</v>
+      </c>
+      <c r="H242" s="3">
+        <v>54</v>
+      </c>
+      <c r="I242" s="3">
+        <v>6</v>
+      </c>
+      <c r="J242" s="3">
         <v>48</v>
-      </c>
-      <c r="C242" s="3">
-        <v>11</v>
-      </c>
-      <c r="D242" s="3">
-        <v>37</v>
-      </c>
-      <c r="E242" t="s">
-        <v>35</v>
-      </c>
-      <c r="F242" t="s">
-        <v>35</v>
-      </c>
-      <c r="G242" t="s">
-        <v>35</v>
-      </c>
-      <c r="H242" t="s">
-        <v>35</v>
-      </c>
-      <c r="I242" t="s">
-        <v>35</v>
-      </c>
-      <c r="J242" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="243" spans="1:10">
       <c r="A243" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B243" s="3">
-        <v>85</v>
+        <v>321</v>
       </c>
       <c r="C243" s="3">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="D243" s="3">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="E243" s="3">
-        <v>31</v>
+        <v>271</v>
       </c>
       <c r="F243" s="3">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="G243" s="3">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="H243" s="3">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I243" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J243" s="3">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="244" spans="1:10">
       <c r="A244" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B244" s="3">
-        <v>321</v>
+        <v>105</v>
       </c>
       <c r="C244" s="3">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="D244" s="3">
-        <v>218</v>
+        <v>68</v>
       </c>
       <c r="E244" s="3">
-        <v>271</v>
+        <v>47</v>
       </c>
       <c r="F244" s="3">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="G244" s="3">
-        <v>183</v>
+        <v>26</v>
       </c>
       <c r="H244" s="3">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I244" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J244" s="3">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="245" spans="1:10">
       <c r="A245" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B245" s="3">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C245" s="3">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D245" s="3">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E245" s="3">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F245" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G245" s="3">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H245" s="3">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="I245" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J245" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246" spans="1:10">
       <c r="A246" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B246" s="3">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="C246" s="3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D246" s="3">
-        <v>38</v>
-      </c>
-      <c r="E246" s="3">
-        <v>55</v>
-      </c>
-      <c r="F246" s="3">
-        <v>20</v>
-      </c>
-      <c r="G246" s="3">
-        <v>35</v>
+        <v>5</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H246" s="3">
         <v>9</v>
       </c>
       <c r="I246" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J246" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:10">
       <c r="A247" t="s">
+        <v>225</v>
+      </c>
+      <c r="B247" s="3">
+        <v>14</v>
+      </c>
+      <c r="C247" t="s">
+        <v>35</v>
+      </c>
+      <c r="D247" t="s">
+        <v>35</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H247" s="3">
+        <v>14</v>
+      </c>
+      <c r="I247" t="s">
+        <v>35</v>
+      </c>
+      <c r="J247" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10">
+      <c r="A248" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B247" s="3">
-        <v>9</v>
-      </c>
-      <c r="C247" s="3">
-        <v>4</v>
-      </c>
-      <c r="D247" s="3">
-        <v>5</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G247" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H247" s="3">
-        <v>9</v>
-      </c>
-      <c r="I247" s="3">
-        <v>4</v>
-      </c>
-      <c r="J247" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="248" spans="1:10">
-      <c r="A248" t="s">
+      <c r="B248" s="1">
+        <v>2546</v>
+      </c>
+      <c r="C248" s="1">
+        <v>772</v>
+      </c>
+      <c r="D248" s="1">
+        <v>1774</v>
+      </c>
+      <c r="E248" s="1">
+        <v>1749</v>
+      </c>
+      <c r="F248" s="1">
+        <v>624</v>
+      </c>
+      <c r="G248" s="1">
+        <v>1125</v>
+      </c>
+      <c r="H248" s="1">
+        <v>797</v>
+      </c>
+      <c r="I248" s="1">
+        <v>148</v>
+      </c>
+      <c r="J248" s="1">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10">
+      <c r="A249" t="s">
         <v>227</v>
       </c>
-      <c r="B248" s="3">
-        <v>14</v>
-      </c>
-      <c r="C248" t="s">
-        <v>35</v>
-      </c>
-      <c r="D248" t="s">
-        <v>35</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G248" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H248" s="3">
-        <v>14</v>
-      </c>
-      <c r="I248" t="s">
-        <v>35</v>
-      </c>
-      <c r="J248" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="249" spans="1:10">
-      <c r="A249" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B249" s="1">
-        <v>2546</v>
-      </c>
-      <c r="C249" s="1">
-        <v>772</v>
-      </c>
-      <c r="D249" s="1">
-        <v>1774</v>
-      </c>
-      <c r="E249" s="1">
-        <v>1749</v>
-      </c>
-      <c r="F249" s="1">
-        <v>624</v>
-      </c>
-      <c r="G249" s="1">
-        <v>1125</v>
-      </c>
-      <c r="H249" s="1">
-        <v>797</v>
-      </c>
-      <c r="I249" s="1">
-        <v>148</v>
-      </c>
-      <c r="J249" s="1">
-        <v>649</v>
+      <c r="B249" s="3">
+        <v>82</v>
+      </c>
+      <c r="C249" s="3">
+        <v>17</v>
+      </c>
+      <c r="D249" s="3">
+        <v>65</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G249" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H249" s="3">
+        <v>82</v>
+      </c>
+      <c r="I249" s="3">
+        <v>17</v>
+      </c>
+      <c r="J249" s="3">
+        <v>65</v>
       </c>
     </row>
     <row r="250" spans="1:10">
       <c r="A250" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B250" s="3">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C250" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D250" s="3">
-        <v>65</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G250" s="2" t="s">
-        <v>4</v>
+        <v>43</v>
+      </c>
+      <c r="E250" s="3">
+        <v>34</v>
+      </c>
+      <c r="F250" s="3">
+        <v>9</v>
+      </c>
+      <c r="G250" s="3">
+        <v>25</v>
       </c>
       <c r="H250" s="3">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="I250" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J250" s="3">
-        <v>65</v>
+        <v>18</v>
       </c>
     </row>
     <row r="251" spans="1:10">
       <c r="A251" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B251" s="3">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C251" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D251" s="3">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E251" s="3">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F251" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G251" s="3">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="H251" s="3">
         <v>22</v>
       </c>
       <c r="I251" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J251" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="252" spans="1:10">
       <c r="A252" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B252" s="3">
-        <v>76</v>
+        <v>476</v>
       </c>
       <c r="C252" s="3">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="D252" s="3">
-        <v>59</v>
+        <v>329</v>
       </c>
       <c r="E252" s="3">
-        <v>54</v>
+        <v>349</v>
       </c>
       <c r="F252" s="3">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="G252" s="3">
-        <v>40</v>
+        <v>232</v>
       </c>
       <c r="H252" s="3">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="I252" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J252" s="3">
-        <v>19</v>
+        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:10">
       <c r="A253" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B253" s="3">
-        <v>476</v>
+        <v>109</v>
       </c>
       <c r="C253" s="3">
-        <v>147</v>
+        <v>15</v>
       </c>
       <c r="D253" s="3">
-        <v>329</v>
+        <v>94</v>
       </c>
       <c r="E253" s="3">
-        <v>349</v>
+        <v>36</v>
       </c>
       <c r="F253" s="3">
-        <v>117</v>
+        <v>6</v>
       </c>
       <c r="G253" s="3">
-        <v>232</v>
+        <v>30</v>
       </c>
       <c r="H253" s="3">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="I253" s="3">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="J253" s="3">
-        <v>97</v>
+        <v>64</v>
       </c>
     </row>
     <row r="254" spans="1:10">
       <c r="A254" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B254" s="3">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="C254" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D254" s="3">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="E254" s="3">
-        <v>36</v>
-      </c>
-      <c r="F254" s="3">
-        <v>6</v>
-      </c>
-      <c r="G254" s="3">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="F254" t="s">
+        <v>35</v>
+      </c>
+      <c r="G254" t="s">
+        <v>35</v>
       </c>
       <c r="H254" s="3">
-        <v>73</v>
-      </c>
-      <c r="I254" s="3">
-        <v>9</v>
-      </c>
-      <c r="J254" s="3">
-        <v>64</v>
+        <v>31</v>
+      </c>
+      <c r="I254" t="s">
+        <v>35</v>
+      </c>
+      <c r="J254" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="255" spans="1:10">
       <c r="A255" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B255" s="3">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="C255" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D255" s="3">
-        <v>66</v>
-      </c>
-      <c r="E255" s="3">
-        <v>44</v>
-      </c>
-      <c r="F255" t="s">
-        <v>35</v>
-      </c>
-      <c r="G255" t="s">
-        <v>35</v>
+        <v>14</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H255" s="3">
-        <v>31</v>
-      </c>
-      <c r="I255" t="s">
-        <v>35</v>
-      </c>
-      <c r="J255" t="s">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="I255" s="3">
+        <v>4</v>
+      </c>
+      <c r="J255" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="256" spans="1:10">
       <c r="A256" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B256" s="3">
+        <v>136</v>
+      </c>
+      <c r="C256" s="3">
+        <v>21</v>
+      </c>
+      <c r="D256" s="3">
+        <v>115</v>
+      </c>
+      <c r="E256" s="3">
         <v>18</v>
       </c>
-      <c r="C256" s="3">
-        <v>4</v>
-      </c>
-      <c r="D256" s="3">
-        <v>14</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G256" s="2" t="s">
-        <v>4</v>
+      <c r="F256" t="s">
+        <v>35</v>
+      </c>
+      <c r="G256" t="s">
+        <v>35</v>
       </c>
       <c r="H256" s="3">
-        <v>18</v>
-      </c>
-      <c r="I256" s="3">
-        <v>4</v>
-      </c>
-      <c r="J256" s="3">
-        <v>14</v>
+        <v>118</v>
+      </c>
+      <c r="I256" t="s">
+        <v>35</v>
+      </c>
+      <c r="J256" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="257" spans="1:10">
       <c r="A257" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B257" s="3">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C257" s="3">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D257" s="3">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="E257" s="3">
-        <v>18</v>
-      </c>
-      <c r="F257" t="s">
-        <v>35</v>
-      </c>
-      <c r="G257" t="s">
-        <v>35</v>
+        <v>87</v>
+      </c>
+      <c r="F257" s="3">
+        <v>31</v>
+      </c>
+      <c r="G257" s="3">
+        <v>56</v>
       </c>
       <c r="H257" s="3">
-        <v>118</v>
-      </c>
-      <c r="I257" t="s">
-        <v>35</v>
-      </c>
-      <c r="J257" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="I257" s="3">
+        <v>5</v>
+      </c>
+      <c r="J257" s="3">
+        <v>36</v>
       </c>
     </row>
     <row r="258" spans="1:10">
       <c r="A258" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="B258" s="3">
-        <v>128</v>
+        <v>1186</v>
       </c>
       <c r="C258" s="3">
-        <v>36</v>
+        <v>457</v>
       </c>
       <c r="D258" s="3">
-        <v>92</v>
+        <v>729</v>
       </c>
       <c r="E258" s="3">
-        <v>87</v>
+        <v>993</v>
       </c>
       <c r="F258" s="3">
-        <v>31</v>
+        <v>404</v>
       </c>
       <c r="G258" s="3">
-        <v>56</v>
+        <v>589</v>
       </c>
       <c r="H258" s="3">
-        <v>41</v>
+        <v>193</v>
       </c>
       <c r="I258" s="3">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="J258" s="3">
-        <v>36</v>
+        <v>140</v>
       </c>
     </row>
     <row r="259" spans="1:10">
       <c r="A259" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B259" s="3">
-        <v>1186</v>
+        <v>204</v>
       </c>
       <c r="C259" s="3">
-        <v>457</v>
+        <v>36</v>
       </c>
       <c r="D259" s="3">
-        <v>729</v>
+        <v>168</v>
       </c>
       <c r="E259" s="3">
-        <v>993</v>
+        <v>134</v>
       </c>
       <c r="F259" s="3">
-        <v>404</v>
+        <v>31</v>
       </c>
       <c r="G259" s="3">
-        <v>589</v>
+        <v>103</v>
       </c>
       <c r="H259" s="3">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="I259" s="3">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="J259" s="3">
-        <v>140</v>
+        <v>65</v>
       </c>
     </row>
     <row r="260" spans="1:10">
-      <c r="A260" t="s">
+      <c r="A260" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B260" s="1">
+        <v>754</v>
+      </c>
+      <c r="C260" s="1">
+        <v>293</v>
+      </c>
+      <c r="D260" s="1">
+        <v>461</v>
+      </c>
+      <c r="E260" s="1">
+        <v>405</v>
+      </c>
+      <c r="F260" s="1">
+        <v>189</v>
+      </c>
+      <c r="G260" s="1">
+        <v>216</v>
+      </c>
+      <c r="H260" s="1">
+        <v>349</v>
+      </c>
+      <c r="I260" s="1">
+        <v>104</v>
+      </c>
+      <c r="J260" s="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10">
+      <c r="A261" t="s">
         <v>238</v>
       </c>
-      <c r="B260" s="3">
-        <v>204</v>
-      </c>
-      <c r="C260" s="3">
-        <v>36</v>
-      </c>
-      <c r="D260" s="3">
-        <v>168</v>
-      </c>
-      <c r="E260" s="3">
-        <v>134</v>
-      </c>
-      <c r="F260" s="3">
-        <v>31</v>
-      </c>
-      <c r="G260" s="3">
-        <v>103</v>
-      </c>
-      <c r="H260" s="3">
-        <v>70</v>
-      </c>
-      <c r="I260" s="3">
-        <v>5</v>
-      </c>
-      <c r="J260" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="261" spans="1:10">
-      <c r="A261" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="B261" s="1">
-        <v>754</v>
-      </c>
-      <c r="C261" s="1">
-        <v>293</v>
-      </c>
-      <c r="D261" s="1">
-        <v>461</v>
-      </c>
-      <c r="E261" s="1">
-        <v>405</v>
-      </c>
-      <c r="F261" s="1">
-        <v>189</v>
-      </c>
-      <c r="G261" s="1">
-        <v>216</v>
-      </c>
-      <c r="H261" s="1">
-        <v>349</v>
-      </c>
-      <c r="I261" s="1">
-        <v>104</v>
-      </c>
-      <c r="J261" s="1">
-        <v>245</v>
+      <c r="B261" s="3">
+        <v>33</v>
+      </c>
+      <c r="C261" t="s">
+        <v>35</v>
+      </c>
+      <c r="D261" t="s">
+        <v>35</v>
+      </c>
+      <c r="E261" s="3">
+        <v>11</v>
+      </c>
+      <c r="F261" t="s">
+        <v>35</v>
+      </c>
+      <c r="G261" t="s">
+        <v>35</v>
+      </c>
+      <c r="H261" s="3">
+        <v>22</v>
+      </c>
+      <c r="I261" t="s">
+        <v>35</v>
+      </c>
+      <c r="J261" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="262" spans="1:10">
       <c r="A262" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B262" s="3">
+        <v>131</v>
+      </c>
+      <c r="C262" s="3">
+        <v>55</v>
+      </c>
+      <c r="D262" s="3">
+        <v>76</v>
+      </c>
+      <c r="E262" s="3">
+        <v>57</v>
+      </c>
+      <c r="F262" s="3">
+        <v>24</v>
+      </c>
+      <c r="G262" s="3">
         <v>33</v>
       </c>
-      <c r="C262" t="s">
-        <v>35</v>
-      </c>
-      <c r="D262" t="s">
-        <v>35</v>
-      </c>
-      <c r="E262" s="3">
-        <v>11</v>
-      </c>
-      <c r="F262" t="s">
-        <v>35</v>
-      </c>
-      <c r="G262" t="s">
-        <v>35</v>
-      </c>
       <c r="H262" s="3">
-        <v>22</v>
-      </c>
-      <c r="I262" t="s">
-        <v>35</v>
-      </c>
-      <c r="J262" t="s">
-        <v>35</v>
+        <v>74</v>
+      </c>
+      <c r="I262" s="3">
+        <v>31</v>
+      </c>
+      <c r="J262" s="3">
+        <v>43</v>
       </c>
     </row>
     <row r="263" spans="1:10">
       <c r="A263" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B263" s="3">
-        <v>131</v>
-      </c>
-      <c r="C263" s="3">
-        <v>55</v>
-      </c>
-      <c r="D263" s="3">
-        <v>76</v>
+        <v>29</v>
+      </c>
+      <c r="C263" t="s">
+        <v>35</v>
+      </c>
+      <c r="D263" t="s">
+        <v>35</v>
       </c>
       <c r="E263" s="3">
-        <v>57</v>
-      </c>
-      <c r="F263" s="3">
-        <v>24</v>
-      </c>
-      <c r="G263" s="3">
-        <v>33</v>
+        <v>11</v>
+      </c>
+      <c r="F263" t="s">
+        <v>35</v>
+      </c>
+      <c r="G263" t="s">
+        <v>35</v>
       </c>
       <c r="H263" s="3">
-        <v>74</v>
-      </c>
-      <c r="I263" s="3">
-        <v>31</v>
-      </c>
-      <c r="J263" s="3">
-        <v>43</v>
+        <v>18</v>
+      </c>
+      <c r="I263" t="s">
+        <v>35</v>
+      </c>
+      <c r="J263" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="264" spans="1:10">
       <c r="A264" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B264" s="3">
-        <v>29</v>
-      </c>
-      <c r="C264" t="s">
-        <v>35</v>
-      </c>
-      <c r="D264" t="s">
-        <v>35</v>
+        <v>159</v>
+      </c>
+      <c r="C264" s="3">
+        <v>39</v>
+      </c>
+      <c r="D264" s="3">
+        <v>120</v>
       </c>
       <c r="E264" s="3">
-        <v>11</v>
-      </c>
-      <c r="F264" t="s">
-        <v>35</v>
-      </c>
-      <c r="G264" t="s">
-        <v>35</v>
+        <v>85</v>
+      </c>
+      <c r="F264" s="3">
+        <v>27</v>
+      </c>
+      <c r="G264" s="3">
+        <v>58</v>
       </c>
       <c r="H264" s="3">
-        <v>18</v>
-      </c>
-      <c r="I264" t="s">
-        <v>35</v>
-      </c>
-      <c r="J264" t="s">
-        <v>35</v>
+        <v>74</v>
+      </c>
+      <c r="I264" s="3">
+        <v>12</v>
+      </c>
+      <c r="J264" s="3">
+        <v>62</v>
       </c>
     </row>
     <row r="265" spans="1:10">
       <c r="A265" t="s">
+        <v>237</v>
+      </c>
+      <c r="B265" s="3">
+        <v>402</v>
+      </c>
+      <c r="C265" s="3">
+        <v>174</v>
+      </c>
+      <c r="D265" s="3">
+        <v>228</v>
+      </c>
+      <c r="E265" s="3">
+        <v>241</v>
+      </c>
+      <c r="F265" s="3">
+        <v>129</v>
+      </c>
+      <c r="G265" s="3">
+        <v>112</v>
+      </c>
+      <c r="H265" s="3">
+        <v>161</v>
+      </c>
+      <c r="I265" s="3">
+        <v>45</v>
+      </c>
+      <c r="J265" s="3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
+      <c r="A266" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B266" s="1">
+        <v>1529</v>
+      </c>
+      <c r="C266" s="1">
+        <v>456</v>
+      </c>
+      <c r="D266" s="1">
+        <v>1073</v>
+      </c>
+      <c r="E266" s="1">
+        <v>1075</v>
+      </c>
+      <c r="F266" s="1">
+        <v>327</v>
+      </c>
+      <c r="G266" s="1">
+        <v>748</v>
+      </c>
+      <c r="H266" s="1">
+        <v>454</v>
+      </c>
+      <c r="I266" s="1">
+        <v>129</v>
+      </c>
+      <c r="J266" s="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
+      <c r="A267" t="s">
         <v>243</v>
       </c>
-      <c r="B265" s="3">
-        <v>159</v>
-      </c>
-      <c r="C265" s="3">
-        <v>39</v>
-      </c>
-      <c r="D265" s="3">
-        <v>120</v>
-      </c>
-      <c r="E265" s="3">
-        <v>85</v>
-      </c>
-      <c r="F265" s="3">
-        <v>27</v>
-      </c>
-      <c r="G265" s="3">
-        <v>58</v>
-      </c>
-      <c r="H265" s="3">
-        <v>74</v>
-      </c>
-      <c r="I265" s="3">
-        <v>12</v>
-      </c>
-      <c r="J265" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="266" spans="1:10">
-      <c r="A266" t="s">
-        <v>239</v>
-      </c>
-      <c r="B266" s="3">
-        <v>402</v>
-      </c>
-      <c r="C266" s="3">
-        <v>174</v>
-      </c>
-      <c r="D266" s="3">
-        <v>228</v>
-      </c>
-      <c r="E266" s="3">
-        <v>241</v>
-      </c>
-      <c r="F266" s="3">
-        <v>129</v>
-      </c>
-      <c r="G266" s="3">
-        <v>112</v>
-      </c>
-      <c r="H266" s="3">
-        <v>161</v>
-      </c>
-      <c r="I266" s="3">
-        <v>45</v>
-      </c>
-      <c r="J266" s="3">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="267" spans="1:10">
-      <c r="A267" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B267" s="1">
-        <v>1529</v>
-      </c>
-      <c r="C267" s="1">
-        <v>456</v>
-      </c>
-      <c r="D267" s="1">
-        <v>1073</v>
-      </c>
-      <c r="E267" s="1">
-        <v>1075</v>
-      </c>
-      <c r="F267" s="1">
-        <v>327</v>
-      </c>
-      <c r="G267" s="1">
-        <v>748</v>
-      </c>
-      <c r="H267" s="1">
-        <v>454</v>
-      </c>
-      <c r="I267" s="1">
-        <v>129</v>
-      </c>
-      <c r="J267" s="1">
-        <v>325</v>
+      <c r="B267" s="3">
+        <v>310</v>
+      </c>
+      <c r="C267" s="3">
+        <v>89</v>
+      </c>
+      <c r="D267" s="3">
+        <v>221</v>
+      </c>
+      <c r="E267" s="3">
+        <v>220</v>
+      </c>
+      <c r="F267" s="3">
+        <v>64</v>
+      </c>
+      <c r="G267" s="3">
+        <v>156</v>
+      </c>
+      <c r="H267" s="3">
+        <v>90</v>
+      </c>
+      <c r="I267" s="3">
+        <v>25</v>
+      </c>
+      <c r="J267" s="3">
+        <v>65</v>
       </c>
     </row>
     <row r="268" spans="1:10">
       <c r="A268" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B268" s="3">
-        <v>310</v>
+        <v>23</v>
       </c>
       <c r="C268" s="3">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="D268" s="3">
-        <v>221</v>
+        <v>14</v>
       </c>
       <c r="E268" s="3">
-        <v>220</v>
+        <v>6</v>
       </c>
       <c r="F268" s="3">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="G268" s="3">
-        <v>156</v>
+        <v>3</v>
       </c>
       <c r="H268" s="3">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="I268" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J268" s="3">
-        <v>65</v>
+        <v>11</v>
       </c>
     </row>
     <row r="269" spans="1:10">
       <c r="A269" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B269" s="3">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C269" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D269" s="3">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="E269" s="3">
-        <v>6</v>
-      </c>
-      <c r="F269" s="3">
-        <v>3</v>
-      </c>
-      <c r="G269" s="3">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="F269" t="s">
+        <v>35</v>
+      </c>
+      <c r="G269" t="s">
+        <v>35</v>
       </c>
       <c r="H269" s="3">
-        <v>17</v>
-      </c>
-      <c r="I269" s="3">
-        <v>6</v>
-      </c>
-      <c r="J269" s="3">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="I269" t="s">
+        <v>35</v>
+      </c>
+      <c r="J269" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="270" spans="1:10">
       <c r="A270" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B270" s="3">
-        <v>80</v>
-      </c>
-      <c r="C270" s="3">
-        <v>6</v>
-      </c>
-      <c r="D270" s="3">
-        <v>74</v>
-      </c>
-      <c r="E270" s="3">
-        <v>60</v>
+        <v>17</v>
+      </c>
+      <c r="C270" t="s">
+        <v>35</v>
+      </c>
+      <c r="D270" t="s">
+        <v>35</v>
+      </c>
+      <c r="E270" t="s">
+        <v>35</v>
       </c>
       <c r="F270" t="s">
         <v>35</v>
@@ -9852,7 +9846,7 @@
         <v>35</v>
       </c>
       <c r="H270" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I270" t="s">
         <v>35</v>
@@ -9863,659 +9857,659 @@
     </row>
     <row r="271" spans="1:10">
       <c r="A271" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B271" s="3">
+        <v>36</v>
+      </c>
+      <c r="C271" s="3">
+        <v>19</v>
+      </c>
+      <c r="D271" s="3">
         <v>17</v>
       </c>
-      <c r="C271" t="s">
-        <v>35</v>
-      </c>
-      <c r="D271" t="s">
-        <v>35</v>
-      </c>
-      <c r="E271" t="s">
-        <v>35</v>
-      </c>
-      <c r="F271" t="s">
-        <v>35</v>
-      </c>
-      <c r="G271" t="s">
-        <v>35</v>
+      <c r="E271" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F271" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H271" s="3">
-        <v>16</v>
-      </c>
-      <c r="I271" t="s">
-        <v>35</v>
-      </c>
-      <c r="J271" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="I271" s="3">
+        <v>19</v>
+      </c>
+      <c r="J271" s="3">
+        <v>17</v>
       </c>
     </row>
     <row r="272" spans="1:10">
       <c r="A272" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B272" s="3">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="C272" s="3">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="D272" s="3">
-        <v>17</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G272" s="2" t="s">
-        <v>4</v>
+        <v>124</v>
+      </c>
+      <c r="E272" s="3">
+        <v>131</v>
+      </c>
+      <c r="F272" s="3">
+        <v>35</v>
+      </c>
+      <c r="G272" s="3">
+        <v>96</v>
       </c>
       <c r="H272" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I272" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="J272" s="3">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="273" spans="1:10">
       <c r="A273" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B273" s="3">
-        <v>164</v>
-      </c>
-      <c r="C273" s="3">
-        <v>40</v>
-      </c>
-      <c r="D273" s="3">
-        <v>124</v>
+        <v>112</v>
+      </c>
+      <c r="C273" t="s">
+        <v>35</v>
+      </c>
+      <c r="D273" t="s">
+        <v>35</v>
       </c>
       <c r="E273" s="3">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="F273" s="3">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G273" s="3">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H273" s="3">
-        <v>33</v>
-      </c>
-      <c r="I273" s="3">
-        <v>5</v>
-      </c>
-      <c r="J273" s="3">
-        <v>28</v>
+        <v>12</v>
+      </c>
+      <c r="I273" t="s">
+        <v>35</v>
+      </c>
+      <c r="J273" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="274" spans="1:10">
       <c r="A274" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B274" s="3">
-        <v>112</v>
-      </c>
-      <c r="C274" t="s">
-        <v>35</v>
-      </c>
-      <c r="D274" t="s">
-        <v>35</v>
-      </c>
-      <c r="E274" s="3">
-        <v>100</v>
-      </c>
-      <c r="F274" s="3">
-        <v>8</v>
-      </c>
-      <c r="G274" s="3">
-        <v>92</v>
+        <v>36</v>
+      </c>
+      <c r="C274" s="3">
+        <v>13</v>
+      </c>
+      <c r="D274" s="3">
+        <v>23</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F274" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H274" s="3">
-        <v>12</v>
-      </c>
-      <c r="I274" t="s">
-        <v>35</v>
-      </c>
-      <c r="J274" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="I274" s="3">
+        <v>13</v>
+      </c>
+      <c r="J274" s="3">
+        <v>23</v>
       </c>
     </row>
     <row r="275" spans="1:10">
       <c r="A275" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B275" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C275" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D275" s="3">
-        <v>23</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G275" s="2" t="s">
-        <v>4</v>
+        <v>29</v>
+      </c>
+      <c r="E275" s="3">
+        <v>20</v>
+      </c>
+      <c r="F275" s="3">
+        <v>6</v>
+      </c>
+      <c r="G275" s="3">
+        <v>14</v>
       </c>
       <c r="H275" s="3">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I275" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J275" s="3">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="276" spans="1:10">
       <c r="A276" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B276" s="3">
-        <v>39</v>
+        <v>168</v>
       </c>
       <c r="C276" s="3">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="D276" s="3">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="E276" s="3">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="F276" s="3">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="G276" s="3">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="H276" s="3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I276" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J276" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="277" spans="1:10">
       <c r="A277" t="s">
+        <v>242</v>
+      </c>
+      <c r="B277" s="3">
+        <v>544</v>
+      </c>
+      <c r="C277" s="3">
+        <v>207</v>
+      </c>
+      <c r="D277" s="3">
+        <v>337</v>
+      </c>
+      <c r="E277" s="3">
+        <v>397</v>
+      </c>
+      <c r="F277" s="3">
+        <v>157</v>
+      </c>
+      <c r="G277" s="3">
+        <v>240</v>
+      </c>
+      <c r="H277" s="3">
+        <v>147</v>
+      </c>
+      <c r="I277" s="3">
+        <v>50</v>
+      </c>
+      <c r="J277" s="3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10">
+      <c r="A278" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B278" s="1">
+        <v>1077</v>
+      </c>
+      <c r="C278" s="1">
+        <v>442</v>
+      </c>
+      <c r="D278" s="1">
+        <v>635</v>
+      </c>
+      <c r="E278" s="1">
+        <v>641</v>
+      </c>
+      <c r="F278" s="1">
+        <v>266</v>
+      </c>
+      <c r="G278" s="1">
+        <v>375</v>
+      </c>
+      <c r="H278" s="1">
+        <v>436</v>
+      </c>
+      <c r="I278" s="1">
+        <v>176</v>
+      </c>
+      <c r="J278" s="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10">
+      <c r="A279" t="s">
         <v>254</v>
       </c>
-      <c r="B277" s="3">
-        <v>168</v>
-      </c>
-      <c r="C277" s="3">
-        <v>52</v>
-      </c>
-      <c r="D277" s="3">
-        <v>116</v>
-      </c>
-      <c r="E277" s="3">
-        <v>140</v>
-      </c>
-      <c r="F277" s="3">
-        <v>49</v>
-      </c>
-      <c r="G277" s="3">
-        <v>91</v>
-      </c>
-      <c r="H277" s="3">
-        <v>28</v>
-      </c>
-      <c r="I277" s="3">
-        <v>3</v>
-      </c>
-      <c r="J277" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="278" spans="1:10">
-      <c r="A278" t="s">
-        <v>244</v>
-      </c>
-      <c r="B278" s="3">
-        <v>544</v>
-      </c>
-      <c r="C278" s="3">
-        <v>207</v>
-      </c>
-      <c r="D278" s="3">
-        <v>337</v>
-      </c>
-      <c r="E278" s="3">
-        <v>397</v>
-      </c>
-      <c r="F278" s="3">
-        <v>157</v>
-      </c>
-      <c r="G278" s="3">
-        <v>240</v>
-      </c>
-      <c r="H278" s="3">
-        <v>147</v>
-      </c>
-      <c r="I278" s="3">
-        <v>50</v>
-      </c>
-      <c r="J278" s="3">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="279" spans="1:10">
-      <c r="A279" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="B279" s="1">
-        <v>1077</v>
-      </c>
-      <c r="C279" s="1">
-        <v>442</v>
-      </c>
-      <c r="D279" s="1">
-        <v>635</v>
-      </c>
-      <c r="E279" s="1">
-        <v>641</v>
-      </c>
-      <c r="F279" s="1">
-        <v>266</v>
-      </c>
-      <c r="G279" s="1">
-        <v>375</v>
-      </c>
-      <c r="H279" s="1">
-        <v>436</v>
-      </c>
-      <c r="I279" s="1">
-        <v>176</v>
-      </c>
-      <c r="J279" s="1">
-        <v>260</v>
+      <c r="B279" s="3">
+        <v>55</v>
+      </c>
+      <c r="C279" s="3">
+        <v>18</v>
+      </c>
+      <c r="D279" s="3">
+        <v>37</v>
+      </c>
+      <c r="E279" s="3">
+        <v>35</v>
+      </c>
+      <c r="F279" s="3">
+        <v>11</v>
+      </c>
+      <c r="G279" s="3">
+        <v>24</v>
+      </c>
+      <c r="H279" s="3">
+        <v>20</v>
+      </c>
+      <c r="I279" s="3">
+        <v>7</v>
+      </c>
+      <c r="J279" s="3">
+        <v>13</v>
       </c>
     </row>
     <row r="280" spans="1:10">
       <c r="A280" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B280" s="3">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C280" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D280" s="3">
-        <v>37</v>
-      </c>
-      <c r="E280" s="3">
-        <v>35</v>
-      </c>
-      <c r="F280" s="3">
-        <v>11</v>
-      </c>
-      <c r="G280" s="3">
-        <v>24</v>
+        <v>17</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F280" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H280" s="3">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I280" s="3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J280" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="281" spans="1:10">
       <c r="A281" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B281" s="3">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C281" s="3">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D281" s="3">
-        <v>17</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G281" s="2" t="s">
-        <v>4</v>
+        <v>33</v>
+      </c>
+      <c r="E281" s="3">
+        <v>21</v>
+      </c>
+      <c r="F281" s="3">
+        <v>6</v>
+      </c>
+      <c r="G281" s="3">
+        <v>15</v>
       </c>
       <c r="H281" s="3">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="I281" s="3">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J281" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="282" spans="1:10">
       <c r="A282" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B282" s="3">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="C282" s="3">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="D282" s="3">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="E282" s="3">
-        <v>21</v>
-      </c>
-      <c r="F282" s="3">
-        <v>6</v>
-      </c>
-      <c r="G282" s="3">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="F282" t="s">
+        <v>35</v>
+      </c>
+      <c r="G282" t="s">
+        <v>35</v>
       </c>
       <c r="H282" s="3">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="I282" s="3">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="J282" s="3">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="283" spans="1:10">
       <c r="A283" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B283" s="3">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="C283" s="3">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="D283" s="3">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E283" s="3">
-        <v>5</v>
-      </c>
-      <c r="F283" t="s">
-        <v>35</v>
-      </c>
-      <c r="G283" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+      <c r="F283" s="3">
+        <v>10</v>
+      </c>
+      <c r="G283" s="3">
+        <v>15</v>
       </c>
       <c r="H283" s="3">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="I283" s="3">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="J283" s="3">
-        <v>55</v>
+        <v>31</v>
       </c>
     </row>
     <row r="284" spans="1:10">
       <c r="A284" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B284" s="3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C284" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D284" s="3">
-        <v>46</v>
-      </c>
-      <c r="E284" s="3">
-        <v>25</v>
-      </c>
-      <c r="F284" s="3">
-        <v>10</v>
-      </c>
-      <c r="G284" s="3">
-        <v>15</v>
+        <v>33</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F284" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G284" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H284" s="3">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="I284" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J284" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="285" spans="1:10">
       <c r="A285" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B285" s="3">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="C285" s="3">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D285" s="3">
-        <v>33</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G285" s="2" t="s">
-        <v>4</v>
+        <v>78</v>
+      </c>
+      <c r="E285" s="3">
+        <v>85</v>
+      </c>
+      <c r="F285" s="3">
+        <v>27</v>
+      </c>
+      <c r="G285" s="3">
+        <v>58</v>
       </c>
       <c r="H285" s="3">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="I285" s="3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J285" s="3">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="286" spans="1:10">
       <c r="A286" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B286" s="3">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="C286" s="3">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D286" s="3">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="E286" s="3">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="F286" s="3">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="G286" s="3">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="H286" s="3">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I286" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J286" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:10">
       <c r="A287" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B287" s="3">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C287" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D287" s="3">
-        <v>26</v>
-      </c>
-      <c r="E287" s="3">
-        <v>28</v>
-      </c>
-      <c r="F287" s="3">
-        <v>10</v>
-      </c>
-      <c r="G287" s="3">
-        <v>18</v>
+        <v>7</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F287" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H287" s="3">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="I287" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J287" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="288" spans="1:10">
       <c r="A288" t="s">
+        <v>253</v>
+      </c>
+      <c r="B288" s="3">
+        <v>521</v>
+      </c>
+      <c r="C288" s="3">
+        <v>221</v>
+      </c>
+      <c r="D288" s="3">
+        <v>300</v>
+      </c>
+      <c r="E288" s="3">
+        <v>442</v>
+      </c>
+      <c r="F288" s="3">
+        <v>200</v>
+      </c>
+      <c r="G288" s="3">
+        <v>242</v>
+      </c>
+      <c r="H288" s="3">
+        <v>79</v>
+      </c>
+      <c r="I288" s="3">
+        <v>21</v>
+      </c>
+      <c r="J288" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10">
+      <c r="A289" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B289" s="1">
+        <v>1060</v>
+      </c>
+      <c r="C289" s="1">
+        <v>318</v>
+      </c>
+      <c r="D289" s="1">
+        <v>742</v>
+      </c>
+      <c r="E289" s="1">
+        <v>728</v>
+      </c>
+      <c r="F289" s="1">
+        <v>237</v>
+      </c>
+      <c r="G289" s="1">
+        <v>491</v>
+      </c>
+      <c r="H289" s="1">
+        <v>332</v>
+      </c>
+      <c r="I289" s="1">
+        <v>81</v>
+      </c>
+      <c r="J289" s="1">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10">
+      <c r="A290" t="s">
         <v>264</v>
       </c>
-      <c r="B288" s="3">
-        <v>30</v>
-      </c>
-      <c r="C288" s="3">
-        <v>23</v>
-      </c>
-      <c r="D288" s="3">
-        <v>7</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G288" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H288" s="3">
-        <v>30</v>
-      </c>
-      <c r="I288" s="3">
-        <v>23</v>
-      </c>
-      <c r="J288" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="289" spans="1:10">
-      <c r="A289" t="s">
-        <v>255</v>
-      </c>
-      <c r="B289" s="3">
-        <v>521</v>
-      </c>
-      <c r="C289" s="3">
-        <v>221</v>
-      </c>
-      <c r="D289" s="3">
-        <v>300</v>
-      </c>
-      <c r="E289" s="3">
-        <v>442</v>
-      </c>
-      <c r="F289" s="3">
-        <v>200</v>
-      </c>
-      <c r="G289" s="3">
-        <v>242</v>
-      </c>
-      <c r="H289" s="3">
-        <v>79</v>
-      </c>
-      <c r="I289" s="3">
+      <c r="B290" s="3">
+        <v>29</v>
+      </c>
+      <c r="C290" s="3">
+        <v>8</v>
+      </c>
+      <c r="D290" s="3">
         <v>21</v>
       </c>
-      <c r="J289" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="290" spans="1:10">
-      <c r="A290" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B290" s="1">
-        <v>1060</v>
-      </c>
-      <c r="C290" s="1">
-        <v>318</v>
-      </c>
-      <c r="D290" s="1">
-        <v>742</v>
-      </c>
-      <c r="E290" s="1">
-        <v>728</v>
-      </c>
-      <c r="F290" s="1">
-        <v>237</v>
-      </c>
-      <c r="G290" s="1">
-        <v>491</v>
-      </c>
-      <c r="H290" s="1">
-        <v>332</v>
-      </c>
-      <c r="I290" s="1">
-        <v>81</v>
-      </c>
-      <c r="J290" s="1">
-        <v>251</v>
+      <c r="E290" s="3">
+        <v>10</v>
+      </c>
+      <c r="F290" t="s">
+        <v>35</v>
+      </c>
+      <c r="G290" t="s">
+        <v>35</v>
+      </c>
+      <c r="H290" s="3">
+        <v>19</v>
+      </c>
+      <c r="I290" t="s">
+        <v>35</v>
+      </c>
+      <c r="J290" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="291" spans="1:10">
       <c r="A291" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B291" s="3">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C291" s="3">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D291" s="3">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E291" s="3">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="F291" t="s">
         <v>35</v>
@@ -10524,7 +10518,7 @@
         <v>35</v>
       </c>
       <c r="H291" s="3">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I291" t="s">
         <v>35</v>
@@ -10535,129 +10529,97 @@
     </row>
     <row r="292" spans="1:10">
       <c r="A292" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B292" s="3">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="C292" s="3">
+        <v>22</v>
+      </c>
+      <c r="D292" s="3">
+        <v>110</v>
+      </c>
+      <c r="E292" s="3">
+        <v>85</v>
+      </c>
+      <c r="F292" s="3">
+        <v>13</v>
+      </c>
+      <c r="G292" s="3">
+        <v>72</v>
+      </c>
+      <c r="H292" s="3">
+        <v>47</v>
+      </c>
+      <c r="I292" s="3">
+        <v>9</v>
+      </c>
+      <c r="J292" s="3">
         <v>38</v>
-      </c>
-      <c r="D292" s="3">
-        <v>59</v>
-      </c>
-      <c r="E292" s="3">
-        <v>57</v>
-      </c>
-      <c r="F292" t="s">
-        <v>35</v>
-      </c>
-      <c r="G292" t="s">
-        <v>35</v>
-      </c>
-      <c r="H292" s="3">
-        <v>40</v>
-      </c>
-      <c r="I292" t="s">
-        <v>35</v>
-      </c>
-      <c r="J292" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="293" spans="1:10">
       <c r="A293" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B293" s="3">
-        <v>132</v>
+        <v>226</v>
       </c>
       <c r="C293" s="3">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D293" s="3">
-        <v>110</v>
-      </c>
-      <c r="E293" s="3">
-        <v>85</v>
-      </c>
-      <c r="F293" s="3">
-        <v>13</v>
-      </c>
-      <c r="G293" s="3">
-        <v>72</v>
+        <v>165</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F293" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="H293" s="3">
-        <v>47</v>
+        <v>226</v>
       </c>
       <c r="I293" s="3">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="J293" s="3">
-        <v>38</v>
+        <v>165</v>
       </c>
     </row>
     <row r="294" spans="1:10">
       <c r="A294" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B294" s="3">
-        <v>226</v>
+        <v>576</v>
       </c>
       <c r="C294" s="3">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="D294" s="3">
-        <v>165</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G294" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H294" s="3">
-        <v>226</v>
-      </c>
-      <c r="I294" s="3">
-        <v>61</v>
-      </c>
-      <c r="J294" s="3">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="295" spans="1:10">
-      <c r="A295" t="s">
-        <v>265</v>
-      </c>
-      <c r="B295" s="3">
+        <v>387</v>
+      </c>
+      <c r="E294" s="3">
         <v>576</v>
       </c>
-      <c r="C295" s="3">
+      <c r="F294" s="3">
         <v>189</v>
       </c>
-      <c r="D295" s="3">
+      <c r="G294" s="3">
         <v>387</v>
       </c>
-      <c r="E295" s="3">
-        <v>576</v>
-      </c>
-      <c r="F295" s="3">
-        <v>189</v>
-      </c>
-      <c r="G295" s="3">
-        <v>387</v>
-      </c>
-      <c r="H295" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I295" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J295" s="2" t="s">
+      <c r="H294" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I294" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J294" s="2" t="s">
         <v>4</v>
       </c>
     </row>
